--- a/public/VendorEmployeesBulkUploadSample.xlsx
+++ b/public/VendorEmployeesBulkUploadSample.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\aman_v2_work\HRMS_Frontend\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\v41797\Desktop\HRMS_FRONTEND\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17527A56-0AEC-41DC-B305-FFE17429573F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB607993-E8E0-44C1-A253-5A6A14323A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{66E3041F-EF95-4E14-9F13-1483DA1BD42E}"/>
+    <workbookView xWindow="4800" yWindow="2810" windowWidth="14400" windowHeight="7270" xr2:uid="{66E3041F-EF95-4E14-9F13-1483DA1BD42E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Ecode</t>
   </si>
@@ -130,6 +130,15 @@
   </si>
   <si>
     <t>ContractorRatePerDay</t>
+  </si>
+  <si>
+    <t>SubDepartment1</t>
+  </si>
+  <si>
+    <t>SubDepartment2</t>
+  </si>
+  <si>
+    <t>SubDepartment3</t>
   </si>
 </sst>
 </file>
@@ -482,42 +491,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0C9055-4F12-402F-8195-1BCB8110DA08}">
-  <dimension ref="A1:AE6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AH6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.81640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="23" max="24" width="5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.7265625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -611,32 +620,41 @@
       <c r="AE1" t="s">
         <v>30</v>
       </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
